--- a/Test upload format/MSME/MSME_Update.xlsx
+++ b/Test upload format/MSME/MSME_Update.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
-  <workbookPr/>
+  <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12180"/>
+    <workbookView windowWidth="24000" windowHeight="9600"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>CGPAN</t>
   </si>
@@ -47,31 +47,16 @@
     <t>NPAInterestAmount</t>
   </si>
   <si>
-    <t>CGMSMGEN0605202600504017</t>
+    <t>CGMSMGEN2109202600357133</t>
   </si>
   <si>
-    <t>loan01</t>
+    <t>QAMSME01</t>
   </si>
   <si>
-    <t>Standard</t>
+    <t>NPA</t>
   </si>
   <si>
-    <t>CGMSMGEN0605202600504018</t>
-  </si>
-  <si>
-    <t>loan02</t>
-  </si>
-  <si>
-    <t>CGMSMGEN0605202600504019</t>
-  </si>
-  <si>
-    <t>loan03</t>
-  </si>
-  <si>
-    <t>CGMSMGEN0605202600504020</t>
-  </si>
-  <si>
-    <t>loan04</t>
+    <t>30-11-2029</t>
   </si>
 </sst>
 </file>
@@ -84,7 +69,7 @@
     <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="179" formatCode="_ &quot;₹&quot;* #,##0_ ;_ &quot;₹&quot;* \-#,##0_ ;_ &quot;₹&quot;* &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="25">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -109,6 +94,12 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Arial"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -458,12 +449,38 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="11">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -567,151 +584,151 @@
   </borders>
   <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0"/>
   </cellStyleXfs>
   <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -727,13 +744,11 @@
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="50">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -993,11 +1008,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr>
+  <sheetPr codeName="Sheet1">
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
-  <sheetFormatPr defaultColWidth="12.6666666666667" defaultRowHeight="12.75" outlineLevelRow="4" outlineLevelCol="5"/>
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr defaultColWidth="12.6666666666667" defaultRowHeight="12.75" outlineLevelRow="1" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="29" style="2" customWidth="1"/>
     <col min="2" max="2" width="23.1047619047619" style="2" customWidth="1"/>
@@ -1038,43 +1053,15 @@
       <c r="C2" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="7"/>
-    </row>
-    <row r="3" ht="15" spans="1:6">
-      <c r="A3" s="5" t="s">
+      <c r="D2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" s="7"/>
-    </row>
-    <row r="4" ht="15" spans="1:6">
-      <c r="A4" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4" s="7"/>
-    </row>
-    <row r="5" ht="15" spans="1:6">
-      <c r="A5" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D5" s="7"/>
+      <c r="E2" s="7">
+        <v>1000000000</v>
+      </c>
+      <c r="F2" s="7">
+        <v>1000000000</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Test upload format/MSME/MSME_Update.xlsx
+++ b/Test upload format/MSME/MSME_Update.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="12">
   <si>
     <t>CGPAN</t>
   </si>
@@ -47,16 +47,22 @@
     <t>NPAInterestAmount</t>
   </si>
   <si>
-    <t>CGMSMGEN2109202600357133</t>
-  </si>
-  <si>
-    <t>QAMSME01</t>
+    <t>CGMSMGEN2209202600357195</t>
+  </si>
+  <si>
+    <t>Aloan04</t>
   </si>
   <si>
     <t>NPA</t>
   </si>
   <si>
-    <t>30-11-2029</t>
+    <t>05-04-2028</t>
+  </si>
+  <si>
+    <t>CGMSMGEN2209202600357207</t>
+  </si>
+  <si>
+    <t>Aloan16</t>
   </si>
 </sst>
 </file>
@@ -449,27 +455,12 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="10">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -605,7 +596,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -617,34 +608,34 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -748,7 +739,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="50">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1011,8 +1002,8 @@
   <sheetPr codeName="Sheet1">
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultColWidth="12.6666666666667" defaultRowHeight="12.75" outlineLevelRow="1" outlineLevelCol="5"/>
+  <dimension ref="A1:F3"/>
+  <sheetFormatPr defaultColWidth="12.6666666666667" defaultRowHeight="12.75" outlineLevelRow="2" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="29" style="2" customWidth="1"/>
     <col min="2" max="2" width="23.1047619047619" style="2" customWidth="1"/>
@@ -1053,14 +1044,34 @@
       <c r="C2" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="7" t="s">
         <v>9</v>
       </c>
       <c r="E2" s="7">
-        <v>1000000000</v>
+        <v>500000000</v>
       </c>
       <c r="F2" s="7">
-        <v>1000000000</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" ht="15" spans="1:6">
+      <c r="A3" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="7">
+        <v>100000000</v>
+      </c>
+      <c r="F3" s="7">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
